--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="425">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -695,7 +695,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -839,7 +842,10 @@
     <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-status</t>
+    <t>Indicates whether the location is still in use.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/location-status|4.0.1</t>
   </si>
   <si>
     <t>.statusCode</t>
@@ -927,7 +933,7 @@
     <t>When using a Location resource for scheduling or orders, we need to be able to refer to a class of Locations instead of a specific Location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-mode</t>
+    <t>http://hl7.org/fhir/ValueSet/location-mode|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity[classCode=PLC].determinerCode</t>
@@ -1266,7 +1272,10 @@
     <t>Indicates which days of the week are available between the start and end Times.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/days-of-week</t>
+    <t>The days of the week.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/days-of-week|4.0.1</t>
   </si>
   <si>
     <t>Location.hoursOfOperation.allDay</t>
@@ -4236,9 +4245,11 @@
       <c r="X24" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>75</v>
@@ -4256,7 +4267,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4271,7 +4282,7 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4279,10 +4290,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4305,19 +4316,19 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4346,7 +4357,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4364,7 +4375,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4379,7 +4390,7 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>75</v>
@@ -4387,10 +4398,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4416,16 +4427,16 @@
         <v>128</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4438,7 +4449,7 @@
         <v>75</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>75</v>
@@ -4474,7 +4485,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4489,7 +4500,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>75</v>
@@ -4497,10 +4508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4526,13 +4537,13 @@
         <v>100</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4546,7 +4557,7 @@
         <v>75</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>75</v>
@@ -4582,7 +4593,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4597,7 +4608,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
@@ -4605,10 +4616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4631,16 +4642,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4690,7 +4701,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4702,10 +4713,10 @@
         <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>75</v>
@@ -4713,10 +4724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4739,16 +4750,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4798,7 +4809,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4810,10 +4821,10 @@
         <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4821,10 +4832,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4850,13 +4861,13 @@
         <v>167</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4884,9 +4895,11 @@
       <c r="X30" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Y30" s="2"/>
+      <c r="Y30" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -4904,7 +4917,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4919,18 +4932,18 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4956,13 +4969,13 @@
         <v>144</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4991,10 +5004,10 @@
         <v>171</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -5012,7 +5025,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5030,15 +5043,15 @@
         <v>152</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5064,13 +5077,13 @@
         <v>100</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5120,7 +5133,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5135,7 +5148,7 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5143,10 +5156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5172,16 +5185,16 @@
         <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5230,7 +5243,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5245,7 +5258,7 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>75</v>
@@ -5253,10 +5266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5282,16 +5295,16 @@
         <v>100</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5340,7 +5353,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5355,7 +5368,7 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5363,10 +5376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5392,16 +5405,16 @@
         <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5428,9 +5441,11 @@
       <c r="X35" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Y35" s="2"/>
+      <c r="Y35" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5448,7 +5463,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5463,18 +5478,18 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5497,16 +5512,16 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5536,7 +5551,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5554,7 +5569,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5569,18 +5584,18 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5603,13 +5618,13 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5660,7 +5675,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5672,10 +5687,10 @@
         <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5683,10 +5698,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5709,19 +5724,19 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5770,7 +5785,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5785,7 +5800,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5793,10 +5808,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5819,19 +5834,19 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5860,7 +5875,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>75</v>
@@ -5878,7 +5893,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5893,18 +5908,18 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5927,17 +5942,17 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -5986,7 +6001,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6001,7 +6016,7 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6009,10 +6024,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6115,10 +6130,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6223,14 +6238,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6252,10 +6267,10 @@
         <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>110</v>
@@ -6310,7 +6325,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6333,10 +6348,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6359,16 +6374,16 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6418,7 +6433,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
@@ -6433,7 +6448,7 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6441,10 +6456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6467,16 +6482,16 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6526,7 +6541,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -6541,7 +6556,7 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6549,10 +6564,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6575,16 +6590,16 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6634,7 +6649,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6649,7 +6664,7 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6657,10 +6672,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6683,19 +6698,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6744,7 +6759,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6756,10 +6771,10 @@
         <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6767,10 +6782,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6793,19 +6808,19 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6854,7 +6869,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6866,10 +6881,10 @@
         <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6877,10 +6892,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6983,10 +6998,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7091,13 +7106,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>75</v>
@@ -7119,13 +7134,13 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7199,10 +7214,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7228,13 +7243,13 @@
         <v>100</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7284,7 +7299,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7293,7 +7308,7 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>97</v>
@@ -7307,10 +7322,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7336,13 +7351,13 @@
         <v>128</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7371,10 +7386,10 @@
         <v>148</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7392,7 +7407,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7415,10 +7430,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7444,13 +7459,13 @@
         <v>204</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7500,7 +7515,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7515,7 +7530,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7523,10 +7538,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7552,13 +7567,13 @@
         <v>100</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7608,7 +7623,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7631,10 +7646,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7657,16 +7672,16 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7716,7 +7731,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7731,7 +7746,7 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7739,10 +7754,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7845,10 +7860,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7953,14 +7968,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7982,10 +7997,10 @@
         <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>110</v>
@@ -8040,7 +8055,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8063,10 +8078,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8092,13 +8107,13 @@
         <v>167</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8126,9 +8141,11 @@
       <c r="X60" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Y60" s="2"/>
+      <c r="Y60" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8146,7 +8163,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8161,7 +8178,7 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8169,10 +8186,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8195,13 +8212,13 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8252,7 +8269,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8267,7 +8284,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8275,10 +8292,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8301,13 +8318,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8358,7 +8375,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8373,7 +8390,7 @@
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8381,10 +8398,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8407,13 +8424,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8464,7 +8481,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8479,7 +8496,7 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8487,10 +8504,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8516,13 +8533,13 @@
         <v>100</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8572,7 +8589,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8595,10 +8612,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8621,19 +8638,19 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8682,7 +8699,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8694,10 +8711,10 @@
         <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -415,7 +415,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -435,7 +435,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -972,7 +972,7 @@
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>If locations can be visited, we need to keep track of their address.</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1127,7 +1127,8 @@
     <t>FR Core Location Part Of Position Room Extension</t>
   </si>
   <si>
-    <t>Position of the bed in the bedroom | Position du lit dans la chambre</t>
+    <t>Position du lit dans la chambre.
+Position of the bed in the bedroom</t>
   </si>
   <si>
     <t>Location.partOf.reference</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -627,6 +627,9 @@
   </si>
   <si>
     <t>FR Core Use Period Extension</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer la période d'utilisation d'une Location.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -3637,7 +3640,7 @@
         <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3697,7 +3700,7 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>114</v>
@@ -3711,10 +3714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3740,16 +3743,16 @@
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3798,7 +3801,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3821,10 +3824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3847,17 +3850,17 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3906,7 +3909,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3921,18 +3924,18 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4035,10 +4038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4143,10 +4146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4172,16 +4175,16 @@
         <v>165</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4206,13 +4209,13 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4230,7 +4233,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4245,7 +4248,7 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
@@ -4253,10 +4256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4279,19 +4282,19 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4320,7 +4323,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4338,7 +4341,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4353,7 +4356,7 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4361,10 +4364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4390,16 +4393,16 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4412,7 +4415,7 @@
         <v>76</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>76</v>
@@ -4448,7 +4451,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4463,7 +4466,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4471,10 +4474,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4500,13 +4503,13 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4520,7 +4523,7 @@
         <v>76</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>76</v>
@@ -4556,7 +4559,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4571,7 +4574,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4579,10 +4582,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4605,13 +4608,13 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4662,7 +4665,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4677,7 +4680,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4685,10 +4688,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4711,16 +4714,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4770,7 +4773,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4785,7 +4788,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -4793,10 +4796,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4822,10 +4825,10 @@
         <v>165</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4852,13 +4855,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -4876,7 +4879,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4891,18 +4894,18 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4928,10 +4931,10 @@
         <v>143</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4961,10 +4964,10 @@
         <v>169</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -4982,7 +4985,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5000,15 +5003,15 @@
         <v>103</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5034,13 +5037,13 @@
         <v>99</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5090,7 +5093,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5105,7 +5108,7 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>76</v>
@@ -5113,10 +5116,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5142,16 +5145,16 @@
         <v>99</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -5200,7 +5203,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5215,7 +5218,7 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5223,10 +5226,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5252,14 +5255,14 @@
         <v>99</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5308,7 +5311,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5323,7 +5326,7 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5331,10 +5334,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5360,16 +5363,16 @@
         <v>165</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5394,13 +5397,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5418,7 +5421,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5433,18 +5436,18 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5467,13 +5470,13 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5504,7 +5507,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5522,7 +5525,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5537,18 +5540,18 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5571,13 +5574,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5628,7 +5631,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5643,7 +5646,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5651,10 +5654,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5677,19 +5680,19 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5738,7 +5741,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5753,7 +5756,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5761,10 +5764,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5787,17 +5790,17 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -5826,7 +5829,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>76</v>
@@ -5844,7 +5847,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5859,18 +5862,18 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5893,17 +5896,17 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -5952,7 +5955,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5967,7 +5970,7 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>76</v>
@@ -5975,10 +5978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6081,10 +6084,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6189,14 +6192,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6218,16 +6221,16 @@
         <v>106</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6276,7 +6279,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6299,10 +6302,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6325,13 +6328,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6382,7 +6385,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6397,7 +6400,7 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
@@ -6405,10 +6408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6431,13 +6434,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6488,7 +6491,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>85</v>
@@ -6503,7 +6506,7 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
@@ -6511,10 +6514,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6537,13 +6540,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6594,7 +6597,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6609,7 +6612,7 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6617,10 +6620,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6643,19 +6646,19 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6704,7 +6707,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6719,7 +6722,7 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
@@ -6727,10 +6730,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6753,17 +6756,17 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6812,7 +6815,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6827,7 +6830,7 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
@@ -6835,10 +6838,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6941,10 +6944,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7049,13 +7052,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="B51" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="C51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>76</v>
@@ -7077,13 +7080,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7157,10 +7160,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7186,13 +7189,13 @@
         <v>99</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7242,7 +7245,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7251,7 +7254,7 @@
         <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>97</v>
@@ -7265,10 +7268,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7294,13 +7297,13 @@
         <v>127</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7329,10 +7332,10 @@
         <v>147</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>76</v>
@@ -7350,7 +7353,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7373,10 +7376,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7399,16 +7402,16 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7458,7 +7461,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7473,7 +7476,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7481,10 +7484,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7510,13 +7513,13 @@
         <v>99</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7566,7 +7569,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7589,10 +7592,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7615,16 +7618,16 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7674,7 +7677,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7689,7 +7692,7 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7697,10 +7700,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7803,10 +7806,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7911,14 +7914,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7940,16 +7943,16 @@
         <v>106</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -7998,7 +8001,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8021,10 +8024,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8050,10 +8053,10 @@
         <v>165</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8080,13 +8083,13 @@
         <v>76</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>76</v>
@@ -8104,7 +8107,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8119,7 +8122,7 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8127,10 +8130,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8153,13 +8156,13 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8210,7 +8213,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8225,7 +8228,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8233,10 +8236,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8259,13 +8262,13 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8316,7 +8319,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8331,7 +8334,7 @@
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8339,10 +8342,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8365,13 +8368,13 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8422,7 +8425,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8437,7 +8440,7 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>76</v>
@@ -8445,10 +8448,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8474,10 +8477,10 @@
         <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8528,7 +8531,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8551,10 +8554,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8577,17 +8580,17 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8636,7 +8639,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -116,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Location|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/location-eu-core|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -679,7 +679,7 @@
 </t>
   </si>
   <si>
-    <t>Unique code or number identifying the location to its users</t>
+    <t>Location identifier</t>
   </si>
   <si>
     <t>Unique code or number identifying the location to its users.</t>
@@ -736,7 +736,7 @@
     <t>Location.name</t>
   </si>
   <si>
-    <t>Name of the location as used by humans</t>
+    <t>Location name</t>
   </si>
   <si>
     <t>Name of the location as used by humans. Does not need to be unique.</t>
@@ -767,7 +767,7 @@
     <t>Location.description</t>
   </si>
   <si>
-    <t>Additional details about the location that could be displayed as further information to identify the location beyond its name</t>
+    <t>Description of the location</t>
   </si>
   <si>
     <t>Description of the Location, which helps in finding or referencing the place.</t>
@@ -829,7 +829,7 @@
 </t>
   </si>
   <si>
-    <t>Contact details of the location</t>
+    <t>Location telecom</t>
   </si>
   <si>
     <t>The contact details of communication devices available at the location. This can include phone numbers, fax numbers, mobile numbers, email addresses and web sites.</t>
@@ -841,7 +841,7 @@
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address
+    <t xml:space="preserve">Address {http://hl7.eu/fhir/base/StructureDefinition/Address-eu|2.0.0}
 </t>
   </si>
   <si>
@@ -863,7 +863,7 @@
     <t>Location.physicalType</t>
   </si>
   <si>
-    <t>Physical form of the location</t>
+    <t>Location type</t>
   </si>
   <si>
     <t>Physical form of the location, e.g. building, room, vehicle, road.</t>
@@ -964,13 +964,13 @@
 </t>
   </si>
   <si>
-    <t>Organization responsible for provisioning and upkeep</t>
+    <t>Managing organization</t>
   </si>
   <si>
     <t>The organization responsible for the provisioning and upkeep of the location.</t>
   </si>
   <si>
-    <t>This can also be used as the part of the organization hierarchy where this location provides services. These services can be defined through the HealthcareService resource.</t>
+    <t>The managing organization is the organization responsible for the location, such as a hospital or clinic.</t>
   </si>
   <si>
     <t>Need to know who manages the location.</t>
@@ -986,7 +986,7 @@
 </t>
   </si>
   <si>
-    <t>Another Location this one is physically a part of</t>
+    <t>Location this one is physically a part of</t>
   </si>
   <si>
     <t>Another Location of which this Location is physically a part of.</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -730,7 +730,7 @@
     <t>The operational status if the location (where typically a bed/room).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0116|2.9</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0116|3.0.0</t>
   </si>
   <si>
     <t>Location.name</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-location.xlsx
+++ b/main/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
